--- a/output/tabellaPsicologa.xlsx
+++ b/output/tabellaPsicologa.xlsx
@@ -8,14 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TheDa\tirocinio\tirocinio\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769AC171-144B-477E-BE26-C9221C5E6C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF29FD8D-85E0-4430-B1CC-E677959526BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{776D536D-3FB0-492C-A107-F9E67A51B7FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{776D536D-3FB0-492C-A107-F9E67A51B7FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$476</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3336" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="47">
   <si>
     <t>sport</t>
   </si>
@@ -125,9 +132,6 @@
     <t>P – LT</t>
   </si>
   <si>
-    <t>R – L</t>
-  </si>
-  <si>
     <t>P – RT</t>
   </si>
   <si>
@@ -177,6 +181,12 @@
   </si>
   <si>
     <t>D-AD</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of posizione</t>
   </si>
 </sst>
 </file>
@@ -265,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -283,6 +293,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -298,6 +309,1560 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="davide gobbo" refreshedDate="46165.526656365742" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="475" xr:uid="{95F48068-0029-4382-8071-DEBCC1275F79}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="E1:E476" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="1">
+    <cacheField name="posizione" numFmtId="0">
+      <sharedItems count="12">
+        <s v="C"/>
+        <s v="P-R"/>
+        <s v="P-L"/>
+        <s v="P-LT"/>
+        <s v="PL-B"/>
+        <s v="P-RT"/>
+        <s v="P-LB"/>
+        <s v="P-RB"/>
+        <s v="P – LT"/>
+        <s v="P – RT"/>
+        <s v="C-L"/>
+        <s v="P-TL"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="475">
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{607FBF84-05E7-4935-8E69-DF4ADAEE71C3}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A2:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of posizione" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -622,31 +2187,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>41</v>
-      </c>
-      <c r="I1" t="s">
-        <v>42</v>
       </c>
       <c r="J1" t="s">
         <v>0</v>
@@ -687,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -722,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -757,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -792,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -827,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -862,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -897,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -932,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -967,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1002,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1037,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1754,7 +3319,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>17</v>
@@ -1807,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1842,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1877,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1912,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2087,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2122,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2157,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2192,7 +3757,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2227,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2262,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2297,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2367,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2402,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2507,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2577,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2612,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2647,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2717,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2752,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2787,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2822,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2857,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2892,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2927,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2962,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3032,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3172,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3207,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3242,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3312,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3347,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3382,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3417,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3452,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3487,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3522,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3557,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3592,7 +5157,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3627,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3662,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3697,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3732,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3767,7 +5332,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3802,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3837,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3872,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3907,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3942,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3977,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4047,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4082,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4117,7 +5682,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4222,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4257,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4327,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4362,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4397,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4432,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4467,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4502,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4537,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4572,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4607,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4642,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4747,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4782,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4817,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4887,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4922,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -4992,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5027,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5062,7 +6627,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5132,7 +6697,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5202,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5482,7 +7047,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5587,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5657,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5727,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5762,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5832,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="K149" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5867,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5902,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -5937,7 +7502,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6007,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6042,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6077,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6112,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6147,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6182,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6217,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6322,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6357,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6427,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6462,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6532,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6567,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6602,7 +8167,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="172" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6637,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="173" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6707,7 +8272,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="175" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6742,7 +8307,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="176" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6847,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="179" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6882,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -6987,7 +8552,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="183" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7022,7 +8587,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="184" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7057,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="185" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7162,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="188" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7197,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="189" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7214,7 +8779,7 @@
         <v>4</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>6</v>
@@ -7232,7 +8797,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7246,7 +8811,7 @@
         <v>9</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>5</v>
@@ -7337,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="193" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7372,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="194" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7407,7 +8972,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="195" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7459,7 +9024,7 @@
         <v>4</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>6</v>
@@ -7512,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="198" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7582,7 +9147,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="200" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7617,7 +9182,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="201" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7652,7 +9217,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="202" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7687,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="203" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7722,7 +9287,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7757,7 +9322,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="205" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7792,7 +9357,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="206" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7879,7 +9444,7 @@
         <v>4</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>6</v>
@@ -7897,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="209" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -7932,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="210" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8037,7 +9602,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="213" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8072,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="214" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8107,7 +9672,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="215" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8142,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="216" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8212,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="218" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8247,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="219" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8282,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8317,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8352,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="222" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8387,7 +9952,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="223" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8422,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="224" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8457,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="225" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8492,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="226" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8527,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8687,7 +10252,7 @@
         <v>5</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>18</v>
@@ -8772,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="234" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8789,7 +10354,7 @@
         <v>10</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>17</v>
@@ -8807,7 +10372,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="235" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8982,7 +10547,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="240" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9017,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="241" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9052,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="242" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9122,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="244" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9192,7 +10757,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="246" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9227,7 +10792,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="247" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9332,7 +10897,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="250" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9367,7 +10932,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="251" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9402,7 +10967,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="252" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9437,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="253" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9472,7 +11037,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="254" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9507,7 +11072,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="255" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9542,7 +11107,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="256" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9577,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="257" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9647,7 +11212,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="259" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9752,7 +11317,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="262" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9787,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="263" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9857,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="265" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9892,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="K265" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="266" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -9997,7 +11562,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="269" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10032,7 +11597,7 @@
         <v>0</v>
       </c>
       <c r="K269" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="270" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10067,7 +11632,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="271" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10102,7 +11667,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="272" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10137,7 +11702,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="273" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10172,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="274" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10207,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="275" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10242,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="276" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10277,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="277" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10312,7 +11877,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="278" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10329,7 +11894,7 @@
         <v>10</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>6</v>
@@ -10347,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="279" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10382,7 +11947,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="280" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10417,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="281" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10452,7 +12017,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="282" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10487,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="283" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10522,7 +12087,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="284" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10557,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="285" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10627,7 +12192,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="287" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10662,7 +12227,7 @@
         <v>0</v>
       </c>
       <c r="K287" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="288" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10697,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="289" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10732,7 +12297,7 @@
         <v>0</v>
       </c>
       <c r="K289" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="290" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10767,7 +12332,7 @@
         <v>0</v>
       </c>
       <c r="K290" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="291" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10802,7 +12367,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="292" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10837,7 +12402,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="293" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10872,7 +12437,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="294" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10907,7 +12472,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="295" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10942,7 +12507,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="296" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -10977,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="297" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11047,7 +12612,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="299" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11292,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="K305" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="306" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11572,7 +13137,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="314" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11607,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="315" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11642,7 +13207,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="316" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11677,7 +13242,7 @@
         <v>0</v>
       </c>
       <c r="K316" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="317" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11712,7 +13277,7 @@
         <v>0</v>
       </c>
       <c r="K317" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="318" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11747,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="319" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11782,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="K319" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="320" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11817,7 +13382,7 @@
         <v>0</v>
       </c>
       <c r="K320" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="321" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11852,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="K321" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="322" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11887,7 +13452,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="323" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11922,7 +13487,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="324" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -11957,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="K324" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="325" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12027,7 +13592,7 @@
         <v>0</v>
       </c>
       <c r="K326" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="327" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12202,7 +13767,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="332" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12295,7 +13860,7 @@
         <v>6</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H334" s="1" t="b">
         <v>0</v>
@@ -12307,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="335" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12342,7 +13907,7 @@
         <v>0</v>
       </c>
       <c r="K335" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="336" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12377,7 +13942,7 @@
         <v>0</v>
       </c>
       <c r="K336" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="337" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12482,7 +14047,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="340" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12517,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="341" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12552,7 +14117,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="342" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12587,7 +14152,7 @@
         <v>0</v>
       </c>
       <c r="K342" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="343" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12622,7 +14187,7 @@
         <v>0</v>
       </c>
       <c r="K343" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="344" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12657,7 +14222,7 @@
         <v>0</v>
       </c>
       <c r="K344" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="345" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12692,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="346" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12727,7 +14292,7 @@
         <v>0</v>
       </c>
       <c r="K346" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="347" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12762,7 +14327,7 @@
         <v>0</v>
       </c>
       <c r="K347" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="348" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12797,7 +14362,7 @@
         <v>0</v>
       </c>
       <c r="K348" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="349" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12867,7 +14432,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="351" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -12972,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="K353" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="354" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13007,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="K354" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="355" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13042,7 +14607,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="356" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13077,7 +14642,7 @@
         <v>0</v>
       </c>
       <c r="K356" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="357" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13112,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="K357" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="358" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13147,7 +14712,7 @@
         <v>0</v>
       </c>
       <c r="K358" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="359" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13182,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="360" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13217,7 +14782,7 @@
         <v>0</v>
       </c>
       <c r="K360" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="361" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13287,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="K362" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="363" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13322,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="K363" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="364" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13357,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="K364" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="365" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13392,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="K365" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="366" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13427,7 +14992,7 @@
         <v>0</v>
       </c>
       <c r="K366" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="367" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13462,7 +15027,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="368" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13497,7 +15062,7 @@
         <v>0</v>
       </c>
       <c r="K368" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="369" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13532,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="K369" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="370" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13567,7 +15132,7 @@
         <v>0</v>
       </c>
       <c r="K370" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="371" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13602,7 +15167,7 @@
         <v>0</v>
       </c>
       <c r="K371" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="372" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13637,7 +15202,7 @@
         <v>0</v>
       </c>
       <c r="K372" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="373" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13672,7 +15237,7 @@
         <v>0</v>
       </c>
       <c r="K373" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="374" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13707,7 +15272,7 @@
         <v>0</v>
       </c>
       <c r="K374" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="375" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13742,7 +15307,7 @@
         <v>0</v>
       </c>
       <c r="K375" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="376" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13777,7 +15342,7 @@
         <v>0</v>
       </c>
       <c r="K376" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="377" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13812,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="K377" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="378" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13847,7 +15412,7 @@
         <v>0</v>
       </c>
       <c r="K378" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="379" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13882,7 +15447,7 @@
         <v>0</v>
       </c>
       <c r="K379" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="380" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13917,7 +15482,7 @@
         <v>0</v>
       </c>
       <c r="K380" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="381" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13952,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="K381" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="382" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -13987,7 +15552,7 @@
         <v>0</v>
       </c>
       <c r="K382" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="383" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14022,7 +15587,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="384" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14057,7 +15622,7 @@
         <v>0</v>
       </c>
       <c r="K384" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="385" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14092,7 +15657,7 @@
         <v>0</v>
       </c>
       <c r="K385" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="386" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14127,7 +15692,7 @@
         <v>0</v>
       </c>
       <c r="K386" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="387" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14162,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="K387" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="388" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14197,7 +15762,7 @@
         <v>0</v>
       </c>
       <c r="K388" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="389" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14232,7 +15797,7 @@
         <v>1</v>
       </c>
       <c r="K389" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="390" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14267,7 +15832,7 @@
         <v>0</v>
       </c>
       <c r="K390" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="391" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14302,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="392" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14337,7 +15902,7 @@
         <v>1</v>
       </c>
       <c r="K392" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="393" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14407,7 +15972,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="395" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14442,7 +16007,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="396" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14477,7 +16042,7 @@
         <v>0</v>
       </c>
       <c r="K396" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="397" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14512,7 +16077,7 @@
         <v>0</v>
       </c>
       <c r="K397" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="398" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14547,7 +16112,7 @@
         <v>0</v>
       </c>
       <c r="K398" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="399" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14582,7 +16147,7 @@
         <v>0</v>
       </c>
       <c r="K399" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="400" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14617,7 +16182,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="401" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14652,7 +16217,7 @@
         <v>0</v>
       </c>
       <c r="K401" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="402" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14687,7 +16252,7 @@
         <v>0</v>
       </c>
       <c r="K402" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="403" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14722,7 +16287,7 @@
         <v>0</v>
       </c>
       <c r="K403" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="404" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14757,7 +16322,7 @@
         <v>0</v>
       </c>
       <c r="K404" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="405" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14792,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="K405" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="406" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14827,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="K406" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="407" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14862,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="K407" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="408" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14897,7 +16462,7 @@
         <v>0</v>
       </c>
       <c r="K408" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="409" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14932,7 +16497,7 @@
         <v>0</v>
       </c>
       <c r="K409" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="410" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -14967,7 +16532,7 @@
         <v>0</v>
       </c>
       <c r="K410" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="411" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15002,7 +16567,7 @@
         <v>0</v>
       </c>
       <c r="K411" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="412" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15037,7 +16602,7 @@
         <v>0</v>
       </c>
       <c r="K412" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="413" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15072,7 +16637,7 @@
         <v>0</v>
       </c>
       <c r="K413" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="414" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15107,7 +16672,7 @@
         <v>0</v>
       </c>
       <c r="K414" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="415" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15142,7 +16707,7 @@
         <v>0</v>
       </c>
       <c r="K415" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="416" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15177,7 +16742,7 @@
         <v>0</v>
       </c>
       <c r="K416" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="417" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15188,7 +16753,7 @@
         <v>8</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>10</v>
@@ -15212,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="K417" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="418" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15247,7 +16812,7 @@
         <v>0</v>
       </c>
       <c r="K418" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="419" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15282,7 +16847,7 @@
         <v>0</v>
       </c>
       <c r="K419" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="420" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15317,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K420" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="421" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15352,7 +16917,7 @@
         <v>0</v>
       </c>
       <c r="K421" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="422" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15387,7 +16952,7 @@
         <v>0</v>
       </c>
       <c r="K422" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="423" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15422,7 +16987,7 @@
         <v>0</v>
       </c>
       <c r="K423" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="424" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15457,7 +17022,7 @@
         <v>0</v>
       </c>
       <c r="K424" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="425" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15492,7 +17057,7 @@
         <v>1</v>
       </c>
       <c r="K425" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="426" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15527,7 +17092,7 @@
         <v>0</v>
       </c>
       <c r="K426" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="427" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15597,7 +17162,7 @@
         <v>1</v>
       </c>
       <c r="K428" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="429" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15632,7 +17197,7 @@
         <v>0</v>
       </c>
       <c r="K429" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="430" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15667,7 +17232,7 @@
         <v>0</v>
       </c>
       <c r="K430" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="431" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15702,7 +17267,7 @@
         <v>0</v>
       </c>
       <c r="K431" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="432" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15737,7 +17302,7 @@
         <v>0</v>
       </c>
       <c r="K432" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="433" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15772,7 +17337,7 @@
         <v>0</v>
       </c>
       <c r="K433" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="434" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15807,7 +17372,7 @@
         <v>0</v>
       </c>
       <c r="K434" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="435" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15842,7 +17407,7 @@
         <v>0</v>
       </c>
       <c r="K435" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="436" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15877,7 +17442,7 @@
         <v>1</v>
       </c>
       <c r="K436" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="437" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15912,7 +17477,7 @@
         <v>0</v>
       </c>
       <c r="K437" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="438" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15947,7 +17512,7 @@
         <v>0</v>
       </c>
       <c r="K438" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="439" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -15982,7 +17547,7 @@
         <v>0</v>
       </c>
       <c r="K439" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="440" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16017,7 +17582,7 @@
         <v>0</v>
       </c>
       <c r="K440" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="441" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16052,7 +17617,7 @@
         <v>0</v>
       </c>
       <c r="K441" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="442" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16087,7 +17652,7 @@
         <v>0</v>
       </c>
       <c r="K442" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="443" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16122,7 +17687,7 @@
         <v>0</v>
       </c>
       <c r="K443" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="444" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16157,7 +17722,7 @@
         <v>0</v>
       </c>
       <c r="K444" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="445" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16192,7 +17757,7 @@
         <v>0</v>
       </c>
       <c r="K445" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="446" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16227,7 +17792,7 @@
         <v>0</v>
       </c>
       <c r="K446" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="447" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16297,7 +17862,7 @@
         <v>1</v>
       </c>
       <c r="K448" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="449" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16332,7 +17897,7 @@
         <v>0</v>
       </c>
       <c r="K449" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="450" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16402,7 +17967,7 @@
         <v>0</v>
       </c>
       <c r="K451" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="452" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16437,7 +18002,7 @@
         <v>0</v>
       </c>
       <c r="K452" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="453" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16472,7 +18037,7 @@
         <v>0</v>
       </c>
       <c r="K453" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="454" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16507,7 +18072,7 @@
         <v>1</v>
       </c>
       <c r="K454" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="455" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16542,7 +18107,7 @@
         <v>1</v>
       </c>
       <c r="K455" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="456" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16577,7 +18142,7 @@
         <v>0</v>
       </c>
       <c r="K456" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="457" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16612,7 +18177,7 @@
         <v>0</v>
       </c>
       <c r="K457" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="458" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16647,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="K458" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="459" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16682,7 +18247,7 @@
         <v>0</v>
       </c>
       <c r="K459" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="460" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16717,7 +18282,7 @@
         <v>0</v>
       </c>
       <c r="K460" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="461" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16752,7 +18317,7 @@
         <v>0</v>
       </c>
       <c r="K461" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="462" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16787,7 +18352,7 @@
         <v>0</v>
       </c>
       <c r="K462" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="463" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16822,7 +18387,7 @@
         <v>0</v>
       </c>
       <c r="K463" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="464" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16857,7 +18422,7 @@
         <v>0</v>
       </c>
       <c r="K464" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="465" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16892,7 +18457,7 @@
         <v>0</v>
       </c>
       <c r="K465" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="466" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16927,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="K466" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="467" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -16997,7 +18562,7 @@
         <v>0</v>
       </c>
       <c r="K468" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="469" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -17032,7 +18597,7 @@
         <v>0</v>
       </c>
       <c r="K469" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="470" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -17067,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K470" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="471" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -17137,7 +18702,7 @@
         <v>0</v>
       </c>
       <c r="K472" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="473" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -17172,7 +18737,7 @@
         <v>0</v>
       </c>
       <c r="K473" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="474" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -17242,7 +18807,7 @@
         <v>0</v>
       </c>
       <c r="K475" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="476" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -17277,7 +18842,134 @@
         <v>0</v>
       </c>
       <c r="K476" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="D1:D476" xr:uid="{C25FBF40-D5DA-4D1A-99FF-E68D4733D7E1}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33ABE9DD-28D5-4ECF-84FD-D303859CCD4E}">
+  <dimension ref="A2:B15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>43</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
